--- a/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>PSTG</t>
   </si>
@@ -656,199 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45326</v>
+      </c>
+      <c r="E7" s="2">
         <v>44962</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44598</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43496</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43131</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42766</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42400</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42035</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41670</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2830600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2753400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2180800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1684200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1643400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1359800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1024800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>739200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>440300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>174500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>42700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>809400</v>
+      </c>
+      <c r="E9" s="3">
         <v>855800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>708300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>535300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>509900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>457500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>353800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>252300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>167900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>77600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2021200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1897600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1472500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1148900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1133600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>902300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>671000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>486900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>272400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>96900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,50 +877,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>736800</v>
+      </c>
+      <c r="E12" s="3">
         <v>692500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>581900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>480500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>433700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>349900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>279200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>245800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>166600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>92700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>36100</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,36 +964,39 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>33600</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>31000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>30000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -990,9 +1009,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1032,9 +1054,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1048,92 +1073,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2777100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2669900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2279200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1945200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1834700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1529100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1192200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>960400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>650500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>354900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>120900</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E18" s="3">
         <v>83500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-98400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-261000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-191300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-169300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-167400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-221300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-210200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-180500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-78100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,118 +1182,125 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E20" s="3">
         <v>13000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>22300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>24500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>13600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>222500</v>
+      </c>
+      <c r="E21" s="3">
         <v>197000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-168700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-77100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-84800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-94200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-169400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-73800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E22" s="3">
         <v>4700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>36700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>31400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>21600</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
@@ -1272,96 +1311,105 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E23" s="3">
         <v>91800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-128500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-270200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-194700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-177300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-156000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-219600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-212200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-181900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-78300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E24" s="3">
         <v>18700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-93400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1401,93 +1449,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E26" s="3">
         <v>73100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-143300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-282100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-201000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-178400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-62600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-221500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-213800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-183200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-78600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E27" s="3">
         <v>73100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-143300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-282100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-201000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-178400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-62600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-221500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-213800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-183200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-78600</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1527,9 +1584,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1542,18 +1602,18 @@
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-97300</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,12 +1626,15 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1611,9 +1674,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1653,93 +1719,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-22300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-24500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-13600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E33" s="3">
         <v>73100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-143300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-282100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-201000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-178400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-159900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-221500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-213800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-183200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-78600</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1779,98 +1854,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E35" s="3">
         <v>73100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-143300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-282100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-201000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-178400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-159900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-221500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-213800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-183200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-78600</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45326</v>
+      </c>
+      <c r="E38" s="2">
         <v>44962</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44598</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43496</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43131</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42766</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42400</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42035</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41670</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1887,8 +1971,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1905,77 +1990,81 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>702500</v>
+      </c>
+      <c r="E41" s="3">
         <v>580900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>466200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>337100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>362600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>448000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>244100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>183700</v>
-      </c>
-      <c r="K41" s="3">
-        <v>604700</v>
       </c>
       <c r="L41" s="3">
         <v>604700</v>
       </c>
       <c r="M41" s="3">
+        <v>604700</v>
+      </c>
+      <c r="N41" s="3">
         <v>130900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>828600</v>
+      </c>
+      <c r="E42" s="3">
         <v>1001400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>947100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>916400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>936500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>749500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>353300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>363000</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1988,177 +2077,192 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>662200</v>
+      </c>
+      <c r="E43" s="3">
         <v>612500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>542100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>460900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>458600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>378700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>243000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>169000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>126300</v>
       </c>
       <c r="L43" s="3">
         <v>126300</v>
       </c>
       <c r="M43" s="3">
+        <v>126300</v>
+      </c>
+      <c r="N43" s="3">
         <v>14800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E44" s="3">
         <v>50200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>38900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>46700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>38500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>44700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>34500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>20600</v>
       </c>
       <c r="L44" s="3">
         <v>20600</v>
       </c>
       <c r="M44" s="3">
+        <v>20600</v>
+      </c>
+      <c r="N44" s="3">
         <v>7900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>262100</v>
+      </c>
+      <c r="E45" s="3">
         <v>230000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>197800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>147000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>94100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>80900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>68600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>40900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>36400</v>
       </c>
       <c r="L45" s="3">
         <v>36400</v>
       </c>
       <c r="M45" s="3">
+        <v>36400</v>
+      </c>
+      <c r="N45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2498100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2474900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2192200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1908200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1890400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1701800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>943500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>780100</v>
-      </c>
-      <c r="K46" s="3">
-        <v>788100</v>
       </c>
       <c r="L46" s="3">
         <v>788100</v>
       </c>
       <c r="M46" s="3">
+        <v>788100</v>
+      </c>
+      <c r="N46" s="3">
         <v>163900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2198,93 +2302,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>482500</v>
+      </c>
+      <c r="E48" s="3">
         <v>431400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>307000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>297700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>235600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>125400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>89100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>81700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>52600</v>
       </c>
       <c r="L48" s="3">
         <v>52600</v>
       </c>
       <c r="M48" s="3">
+        <v>52600</v>
+      </c>
+      <c r="N48" s="3">
         <v>12200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>394400</v>
+      </c>
+      <c r="E49" s="3">
         <v>410600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>421400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>435400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>95800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>31100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6600</v>
-      </c>
-      <c r="K49" s="3">
-        <v>7000</v>
       </c>
       <c r="L49" s="3">
         <v>7000</v>
       </c>
       <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+        <v>7000</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2324,9 +2437,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2366,51 +2482,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>280700</v>
+      </c>
+      <c r="E52" s="3">
         <v>226600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>214700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>178200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>142400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>114700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>86300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>23100</v>
       </c>
       <c r="L52" s="3">
         <v>23100</v>
       </c>
       <c r="M52" s="3">
+        <v>23100</v>
+      </c>
+      <c r="N52" s="3">
         <v>8900</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2450,51 +2572,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3655800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3543500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3135300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2819400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2364200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1973000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1124000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>899700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>870800</v>
       </c>
       <c r="L54" s="3">
         <v>870800</v>
       </c>
       <c r="M54" s="3">
+        <v>870800</v>
+      </c>
+      <c r="N54" s="3">
         <v>185000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2511,8 +2639,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2529,59 +2658,63 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E57" s="3">
         <v>67100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>70700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>77700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>103500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>52700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>38200</v>
       </c>
       <c r="L57" s="3">
         <v>38200</v>
       </c>
       <c r="M57" s="3">
+        <v>38200</v>
+      </c>
+      <c r="N57" s="3">
         <v>7500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
         <v>579900</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2597,8 +2730,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2612,114 +2745,123 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1278700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1102800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>881600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>693100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>537100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>406400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>278300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>220400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>146300</v>
       </c>
       <c r="L59" s="3">
         <v>146300</v>
       </c>
       <c r="M59" s="3">
+        <v>146300</v>
+      </c>
+      <c r="N59" s="3">
         <v>21600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1365700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1749900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>952300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>760700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>614700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>509800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>362700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>273100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>184500</v>
       </c>
       <c r="L60" s="3">
         <v>184500</v>
       </c>
       <c r="M60" s="3">
+        <v>184500</v>
+      </c>
+      <c r="N60" s="3">
         <v>29200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>786800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>755800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>477000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>449800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2738,51 +2880,57 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>919800</v>
+      </c>
+      <c r="E62" s="3">
         <v>847600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>641900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>553000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>442300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>275600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>186900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>148200</v>
-      </c>
-      <c r="K62" s="3">
-        <v>122900</v>
       </c>
       <c r="L62" s="3">
         <v>122900</v>
       </c>
       <c r="M62" s="3">
+        <v>122900</v>
+      </c>
+      <c r="N62" s="3">
         <v>9000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2822,9 +2970,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2864,9 +3015,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2906,51 +3060,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2385700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2602200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2381000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2069400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1534100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1235200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>549600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>421300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>307400</v>
       </c>
       <c r="L66" s="3">
         <v>307400</v>
       </c>
       <c r="M66" s="3">
+        <v>307400</v>
+      </c>
+      <c r="N66" s="3">
         <v>38100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2967,8 +3127,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3008,9 +3169,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3050,9 +3214,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3084,17 +3251,20 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>263000</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3134,51 +3304,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1475800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1537100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1708300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1565000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1282900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1081900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-903600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-802500</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-555300</v>
       </c>
       <c r="L72" s="3">
         <v>-555300</v>
       </c>
       <c r="M72" s="3">
+        <v>-555300</v>
+      </c>
+      <c r="N72" s="3">
         <v>-128200</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3218,9 +3394,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3260,9 +3439,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3302,51 +3484,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1270100</v>
+      </c>
+      <c r="E76" s="3">
         <v>941200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>754300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>750000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>830100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>737800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>574400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>478400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>563400</v>
       </c>
       <c r="L76" s="3">
         <v>563400</v>
       </c>
       <c r="M76" s="3">
+        <v>563400</v>
+      </c>
+      <c r="N76" s="3">
         <v>-116100</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3386,98 +3574,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45326</v>
+      </c>
+      <c r="E80" s="2">
         <v>44962</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44598</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43496</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43131</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42766</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42400</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42035</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41670</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E81" s="3">
         <v>73100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-143300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-282100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-201000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-178400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-159900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-221500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-213800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-183200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-78600</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3494,50 +3691,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>124400</v>
+      </c>
+      <c r="E83" s="3">
         <v>100400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>83200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>70000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>89700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>70900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>61700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>50200</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>4400</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3577,9 +3778,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3619,9 +3823,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3661,9 +3868,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3703,9 +3913,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3745,51 +3958,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>677700</v>
+      </c>
+      <c r="E89" s="3">
         <v>767200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>410100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>187600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>189600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>164400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>72800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14400</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-143700</v>
       </c>
       <c r="L89" s="3">
         <v>-143700</v>
       </c>
       <c r="M89" s="3">
+        <v>-143700</v>
+      </c>
+      <c r="N89" s="3">
         <v>-67200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3806,50 +4025,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-195200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-158100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-102300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-95000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-87800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-76800</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-42200</v>
       </c>
       <c r="L91" s="3">
         <v>-42200</v>
       </c>
       <c r="M91" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-12300</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3889,9 +4112,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3931,51 +4157,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-221400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-153300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-418100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-324700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-511300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-441600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-15300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3992,8 +4224,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4033,9 +4266,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4075,9 +4311,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4117,9 +4356,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4159,51 +4401,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-560200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-431200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-127800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>49200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>551900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>46800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>163300</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4228,14 +4476,14 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4243,49 +4491,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E102" s="3">
         <v>114700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>129100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-85900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>205000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>62400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-415500</v>
-      </c>
-      <c r="K102" s="3">
-        <v>61800</v>
       </c>
       <c r="L102" s="3">
         <v>61800</v>
       </c>
       <c r="M102" s="3">
+        <v>61800</v>
+      </c>
+      <c r="N102" s="3">
         <v>80800</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>PSTG</t>
   </si>
@@ -784,7 +784,7 @@
         <v>708300</v>
       </c>
       <c r="G9" s="3">
-        <v>535300</v>
+        <v>534400</v>
       </c>
       <c r="H9" s="3">
         <v>509900</v>
@@ -829,7 +829,7 @@
         <v>1472500</v>
       </c>
       <c r="G10" s="3">
-        <v>1148900</v>
+        <v>1149800</v>
       </c>
       <c r="H10" s="3">
         <v>1133600</v>
@@ -976,23 +976,23 @@
       <c r="D14" s="3">
         <v>33600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>31000</v>
+        <v>31900</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>30000</v>
@@ -1019,25 +1019,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>124400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>83200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>70000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>89700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>68300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>60200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2777100</v>
+        <v>2743500</v>
       </c>
       <c r="E17" s="3">
         <v>2669900</v>
@@ -1089,7 +1089,7 @@
         <v>2279200</v>
       </c>
       <c r="G17" s="3">
-        <v>1945200</v>
+        <v>1913300</v>
       </c>
       <c r="H17" s="3">
         <v>1834700</v>
@@ -1125,7 +1125,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>53600</v>
+        <v>87200</v>
       </c>
       <c r="E18" s="3">
         <v>83500</v>
@@ -1134,7 +1134,7 @@
         <v>-98400</v>
       </c>
       <c r="G18" s="3">
-        <v>-261000</v>
+        <v>-229100</v>
       </c>
       <c r="H18" s="3">
         <v>-191300</v>
@@ -1189,25 +1189,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>44500</v>
+        <v>5900</v>
       </c>
       <c r="E20" s="3">
-        <v>13000</v>
+        <v>4300</v>
       </c>
       <c r="F20" s="3">
-        <v>6600</v>
+        <v>2800</v>
       </c>
       <c r="G20" s="3">
-        <v>22300</v>
+        <v>-4800</v>
       </c>
       <c r="H20" s="3">
-        <v>24500</v>
+        <v>2700</v>
       </c>
       <c r="I20" s="3">
-        <v>13600</v>
+        <v>4400</v>
       </c>
       <c r="J20" s="3">
-        <v>11500</v>
+        <v>-6000</v>
       </c>
       <c r="K20" s="3">
         <v>1700</v>
@@ -1234,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>222500</v>
+        <v>205700</v>
       </c>
       <c r="E21" s="3">
-        <v>197000</v>
+        <v>179700</v>
       </c>
       <c r="F21" s="3">
-        <v>-8700</v>
+        <v>-18000</v>
       </c>
       <c r="G21" s="3">
-        <v>-168700</v>
+        <v>-154300</v>
       </c>
       <c r="H21" s="3">
-        <v>-77100</v>
+        <v>-104300</v>
       </c>
       <c r="I21" s="3">
-        <v>-84800</v>
+        <v>-105400</v>
       </c>
       <c r="J21" s="3">
-        <v>-94200</v>
+        <v>-101200</v>
       </c>
       <c r="K21" s="3">
         <v>-169400</v>
@@ -1387,7 +1387,7 @@
         <v>1100</v>
       </c>
       <c r="J24" s="3">
-        <v>-93400</v>
+        <v>3900</v>
       </c>
       <c r="K24" s="3">
         <v>1900</v>
@@ -1477,7 +1477,7 @@
         <v>-178400</v>
       </c>
       <c r="J26" s="3">
-        <v>-62600</v>
+        <v>-159900</v>
       </c>
       <c r="K26" s="3">
         <v>-221500</v>
@@ -1522,7 +1522,7 @@
         <v>-178400</v>
       </c>
       <c r="J27" s="3">
-        <v>-62600</v>
+        <v>-159900</v>
       </c>
       <c r="K27" s="3">
         <v>-221500</v>
@@ -1593,17 +1593,17 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-97300</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1729,25 +1729,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-44500</v>
+        <v>-5900</v>
       </c>
       <c r="E32" s="3">
-        <v>-13000</v>
+        <v>-4300</v>
       </c>
       <c r="F32" s="3">
-        <v>-6600</v>
+        <v>-2800</v>
       </c>
       <c r="G32" s="3">
-        <v>-22300</v>
+        <v>4800</v>
       </c>
       <c r="H32" s="3">
-        <v>-24500</v>
+        <v>-2700</v>
       </c>
       <c r="I32" s="3">
-        <v>-13600</v>
+        <v>-4400</v>
       </c>
       <c r="J32" s="3">
-        <v>-11500</v>
+        <v>6000</v>
       </c>
       <c r="K32" s="3">
         <v>-1700</v>
@@ -2177,25 +2177,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>262100</v>
+        <v>88700</v>
       </c>
       <c r="E45" s="3">
-        <v>230000</v>
+        <v>68600</v>
       </c>
       <c r="F45" s="3">
-        <v>197800</v>
+        <v>81600</v>
       </c>
       <c r="G45" s="3">
-        <v>147000</v>
+        <v>57200</v>
       </c>
       <c r="H45" s="3">
-        <v>94100</v>
+        <v>37100</v>
       </c>
       <c r="I45" s="3">
-        <v>80900</v>
+        <v>29200</v>
       </c>
       <c r="J45" s="3">
-        <v>68600</v>
+        <v>21100</v>
       </c>
       <c r="K45" s="3">
         <v>40900</v>
@@ -2266,26 +2266,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2492,25 +2492,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>280700</v>
+        <v>65100</v>
       </c>
       <c r="E52" s="3">
-        <v>226600</v>
+        <v>49400</v>
       </c>
       <c r="F52" s="3">
-        <v>214700</v>
+        <v>50000</v>
       </c>
       <c r="G52" s="3">
-        <v>178200</v>
+        <v>47400</v>
       </c>
       <c r="H52" s="3">
-        <v>142400</v>
+        <v>40300</v>
       </c>
       <c r="I52" s="3">
-        <v>114700</v>
+        <v>29000</v>
       </c>
       <c r="J52" s="3">
-        <v>86300</v>
+        <v>19000</v>
       </c>
       <c r="K52" s="3">
         <v>31400</v>
@@ -2710,25 +2710,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4200</v>
+        <v>48900</v>
       </c>
       <c r="E58" s="3">
-        <v>579900</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>613600</v>
+      </c>
+      <c r="F58" s="3">
+        <v>36100</v>
+      </c>
+      <c r="G58" s="3">
+        <v>32200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>27300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2755,25 +2755,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1278700</v>
+        <v>889900</v>
       </c>
       <c r="E59" s="3">
-        <v>1102800</v>
+        <v>756100</v>
       </c>
       <c r="F59" s="3">
-        <v>881600</v>
+        <v>584500</v>
       </c>
       <c r="G59" s="3">
-        <v>693100</v>
+        <v>452000</v>
       </c>
       <c r="H59" s="3">
-        <v>537100</v>
+        <v>371200</v>
       </c>
       <c r="I59" s="3">
-        <v>406400</v>
+        <v>277500</v>
       </c>
       <c r="J59" s="3">
-        <v>278300</v>
+        <v>195300</v>
       </c>
       <c r="K59" s="3">
         <v>220400</v>
@@ -2845,19 +2845,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100200</v>
+        <v>223400</v>
       </c>
       <c r="E61" s="3">
-        <v>4800</v>
+        <v>147200</v>
       </c>
       <c r="F61" s="3">
-        <v>786800</v>
+        <v>881700</v>
       </c>
       <c r="G61" s="3">
-        <v>755800</v>
+        <v>876200</v>
       </c>
       <c r="H61" s="3">
-        <v>477000</v>
+        <v>570000</v>
       </c>
       <c r="I61" s="3">
         <v>449800</v>
@@ -2890,25 +2890,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>919800</v>
+        <v>54300</v>
       </c>
       <c r="E62" s="3">
-        <v>847600</v>
+        <v>37600</v>
       </c>
       <c r="F62" s="3">
-        <v>641900</v>
+        <v>29600</v>
       </c>
       <c r="G62" s="3">
-        <v>553000</v>
+        <v>27200</v>
       </c>
       <c r="H62" s="3">
-        <v>442300</v>
+        <v>8100</v>
       </c>
       <c r="I62" s="3">
-        <v>275600</v>
+        <v>6300</v>
       </c>
       <c r="J62" s="3">
-        <v>186900</v>
+        <v>4000</v>
       </c>
       <c r="K62" s="3">
         <v>148200</v>
@@ -3698,25 +3698,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>124400</v>
+        <v>108200</v>
       </c>
       <c r="E83" s="3">
-        <v>100400</v>
+        <v>83900</v>
       </c>
       <c r="F83" s="3">
-        <v>83200</v>
+        <v>66400</v>
       </c>
       <c r="G83" s="3">
-        <v>70000</v>
+        <v>57000</v>
       </c>
       <c r="H83" s="3">
-        <v>89700</v>
+        <v>80400</v>
       </c>
       <c r="I83" s="3">
-        <v>70900</v>
+        <v>68300</v>
       </c>
       <c r="J83" s="3">
-        <v>61700</v>
+        <v>60200</v>
       </c>
       <c r="K83" s="3">
         <v>50200</v>
@@ -4455,26 +4455,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>PSTG</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
         <v>45326</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44598</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43496</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43131</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42766</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42400</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42035</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41670</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3168200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2830600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2753400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2180800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1684200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1643400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1359800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1024800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>739200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>440300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>174500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42700</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>949700</v>
+      </c>
+      <c r="E9" s="3">
         <v>809400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>855800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>708300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>534400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>509900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>457500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>353800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>252300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>167900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2218400</v>
+      </c>
+      <c r="E10" s="3">
         <v>2021200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1897600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1472500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1149800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1133600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>902300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>671000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>486900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>272400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>96900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,53 +890,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>804400</v>
+      </c>
+      <c r="E12" s="3">
         <v>736800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>692500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>581900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>480500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>433700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>349900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>279200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>245800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>166600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>92700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>36100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -967,39 +983,42 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E14" s="3">
         <v>33600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>31900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>30000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1012,36 +1031,39 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E15" s="3">
         <v>124400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>83200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>70000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>89700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>68300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>60200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1057,9 +1079,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3066400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2743500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2669900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2279200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1913300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1834700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1529100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1192200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>960400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>650500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>354900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>120900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E18" s="3">
         <v>87200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>83500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-98400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-229100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-191300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-169300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-167400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-221300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-210200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-180500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-78100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1183,127 +1215,134 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-62600</v>
+      </c>
+      <c r="E20" s="3">
         <v>5900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E21" s="3">
         <v>205700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>179700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-154300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-104300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-105400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-101200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-169400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-73800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
         <v>7500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>36700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>21600</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1314,102 +1353,111 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E23" s="3">
         <v>90600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>91800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-128500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-270200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-194700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-177300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-156000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-219600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-212200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-181900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-78300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E24" s="3">
         <v>29300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E26" s="3">
         <v>61300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>73100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-143300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-282100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-201000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-178400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-159900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-221500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-213800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-183200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-78600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E27" s="3">
         <v>61300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>73100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-143300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-282100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-201000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-178400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-159900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-221500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-213800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-183200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-78600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1587,9 +1644,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1674,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1629,12 +1689,15 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E33" s="3">
         <v>61300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>73100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-143300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-282100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-201000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-178400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-159900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-221500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-213800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-183200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-78600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E35" s="3">
         <v>61300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>73100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-143300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-282100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-201000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-178400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-159900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-221500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-213800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-183200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-78600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
         <v>45326</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44598</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43496</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43131</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42766</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42400</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42035</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41670</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1991,83 +2076,87 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>723600</v>
+      </c>
+      <c r="E41" s="3">
         <v>702500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>580900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>466200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>337100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>362600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>448000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>244100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>183700</v>
-      </c>
-      <c r="L41" s="3">
-        <v>604700</v>
       </c>
       <c r="M41" s="3">
         <v>604700</v>
       </c>
       <c r="N41" s="3">
+        <v>604700</v>
+      </c>
+      <c r="O41" s="3">
         <v>130900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>798200</v>
+      </c>
+      <c r="E42" s="3">
         <v>828600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1001400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>947100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>916400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>936500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>749500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>353300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>363000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,189 +2169,204 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>680900</v>
+      </c>
+      <c r="E43" s="3">
         <v>662200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>612500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>542100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>460900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>458600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>378700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>243000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>169000</v>
-      </c>
-      <c r="L43" s="3">
-        <v>126300</v>
       </c>
       <c r="M43" s="3">
         <v>126300</v>
       </c>
       <c r="N43" s="3">
+        <v>126300</v>
+      </c>
+      <c r="O43" s="3">
         <v>14800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E44" s="3">
         <v>42700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>50200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>38900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>46700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>38500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>44700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>34500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>20600</v>
       </c>
       <c r="M44" s="3">
         <v>20600</v>
       </c>
       <c r="N44" s="3">
+        <v>20600</v>
+      </c>
+      <c r="O44" s="3">
         <v>7900</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E45" s="3">
         <v>88700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>68600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>81600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>57200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>29200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>40900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>36400</v>
       </c>
       <c r="M45" s="3">
         <v>36400</v>
       </c>
       <c r="N45" s="3">
+        <v>36400</v>
+      </c>
+      <c r="O45" s="3">
         <v>10300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2567300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2498100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2474900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2192200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1908200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1890400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1701800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>943500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>780100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>788100</v>
       </c>
       <c r="M46" s="3">
         <v>788100</v>
       </c>
       <c r="N46" s="3">
+        <v>788100</v>
+      </c>
+      <c r="O46" s="3">
         <v>163900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2287,8 +2391,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2305,99 +2409,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>608400</v>
+      </c>
+      <c r="E48" s="3">
         <v>482500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>431400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>307000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>297700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>235600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>125400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>89100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>81700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>52600</v>
       </c>
       <c r="M48" s="3">
         <v>52600</v>
       </c>
       <c r="N48" s="3">
+        <v>52600</v>
+      </c>
+      <c r="O48" s="3">
         <v>12200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>380500</v>
+      </c>
+      <c r="E49" s="3">
         <v>394400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>410600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>421400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>435400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>95800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>31100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>7000</v>
       </c>
       <c r="M49" s="3">
         <v>7000</v>
       </c>
       <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+        <v>7000</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2601,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>178400</v>
+      </c>
+      <c r="E52" s="3">
         <v>65100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>49400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>50000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>47400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>29000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>23100</v>
       </c>
       <c r="M52" s="3">
         <v>23100</v>
       </c>
       <c r="N52" s="3">
+        <v>23100</v>
+      </c>
+      <c r="O52" s="3">
         <v>8900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3963900</v>
+      </c>
+      <c r="E54" s="3">
         <v>3655800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3543500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3135300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2819400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2364200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1973000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1124000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>899700</v>
-      </c>
-      <c r="L54" s="3">
-        <v>870800</v>
       </c>
       <c r="M54" s="3">
         <v>870800</v>
       </c>
       <c r="N54" s="3">
+        <v>870800</v>
+      </c>
+      <c r="O54" s="3">
         <v>185000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,82 +2788,86 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E57" s="3">
         <v>82800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>70700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>77700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>103500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>84400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>52700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>38200</v>
       </c>
       <c r="M57" s="3">
         <v>38200</v>
       </c>
       <c r="N57" s="3">
+        <v>38200</v>
+      </c>
+      <c r="O57" s="3">
         <v>7500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E58" s="3">
         <v>48900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>613600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>36100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>27300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2748,123 +2881,132 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>953800</v>
+      </c>
+      <c r="E59" s="3">
         <v>889900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>756100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>584500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>452000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>371200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>277500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>195300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>220400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>146300</v>
       </c>
       <c r="M59" s="3">
         <v>146300</v>
       </c>
       <c r="N59" s="3">
+        <v>146300</v>
+      </c>
+      <c r="O59" s="3">
         <v>21600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1596500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1365700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1749900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>952300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>760700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>614700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>509800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>362700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>273100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>184500</v>
       </c>
       <c r="M60" s="3">
         <v>184500</v>
       </c>
       <c r="N60" s="3">
+        <v>184500</v>
+      </c>
+      <c r="O60" s="3">
         <v>29200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E61" s="3">
         <v>223400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>147200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>881700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>876200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>570000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>449800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2883,54 +3025,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E62" s="3">
         <v>54300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>37600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>148200</v>
-      </c>
-      <c r="L62" s="3">
-        <v>122900</v>
       </c>
       <c r="M62" s="3">
         <v>122900</v>
       </c>
       <c r="N62" s="3">
+        <v>122900</v>
+      </c>
+      <c r="O62" s="3">
         <v>9000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2657500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2385700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2602200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2381000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2069400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1534100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1235200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>549600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>421300</v>
-      </c>
-      <c r="L66" s="3">
-        <v>307400</v>
       </c>
       <c r="M66" s="3">
         <v>307400</v>
       </c>
       <c r="N66" s="3">
+        <v>307400</v>
+      </c>
+      <c r="O66" s="3">
         <v>38100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3254,17 +3421,20 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>263000</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1369000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1475800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1537100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1708300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1565000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1282900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1081900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-903600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-802500</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-555300</v>
       </c>
       <c r="M72" s="3">
         <v>-555300</v>
       </c>
       <c r="N72" s="3">
+        <v>-555300</v>
+      </c>
+      <c r="O72" s="3">
         <v>-128200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1306500</v>
+      </c>
+      <c r="E76" s="3">
         <v>1270100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>941200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>754300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>750000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>830100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>737800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>574400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>478400</v>
-      </c>
-      <c r="L76" s="3">
-        <v>563400</v>
       </c>
       <c r="M76" s="3">
         <v>563400</v>
       </c>
       <c r="N76" s="3">
+        <v>563400</v>
+      </c>
+      <c r="O76" s="3">
         <v>-116100</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
         <v>45326</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44598</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43496</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43131</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42766</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42400</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42035</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41670</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E81" s="3">
         <v>61300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>73100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-143300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-282100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-201000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-178400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-159900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-221500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-213800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-183200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-78600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E83" s="3">
         <v>108200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>83900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>66400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>57000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>80400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>68300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>60200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>50200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
         <v>4400</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>753100</v>
+      </c>
+      <c r="E89" s="3">
         <v>677700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>767200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>410100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>187600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>189600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>164400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>72800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14400</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-143700</v>
       </c>
       <c r="M89" s="3">
         <v>-143700</v>
       </c>
       <c r="N89" s="3">
+        <v>-143700</v>
+      </c>
+      <c r="O89" s="3">
         <v>-67200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-226700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-195200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-158100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-102300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-95000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-87800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-76800</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-42200</v>
       </c>
       <c r="M91" s="3">
         <v>-42200</v>
       </c>
       <c r="N91" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-12300</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-217700</v>
+      </c>
+      <c r="E94" s="3">
         <v>3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-221400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-153300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-418100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-324700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-511300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-441600</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-15300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,8 +4457,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4269,9 +4502,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,54 +4646,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-509800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-560200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-431200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-127800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>49200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>551900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>46800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>163300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4476,17 +4724,17 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -4494,52 +4742,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E102" s="3">
         <v>120700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>114700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>129100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-85900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>205000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>62400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-415500</v>
-      </c>
-      <c r="L102" s="3">
-        <v>61800</v>
       </c>
       <c r="M102" s="3">
         <v>61800</v>
       </c>
       <c r="N102" s="3">
+        <v>61800</v>
+      </c>
+      <c r="O102" s="3">
         <v>80800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PSTG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>PSTG</t>
   </si>
@@ -781,7 +781,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>949700</v>
+        <v>955500</v>
       </c>
       <c r="E9" s="3">
         <v>809400</v>
@@ -829,7 +829,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>2218400</v>
+        <v>2212700</v>
       </c>
       <c r="E10" s="3">
         <v>2021200</v>
@@ -993,7 +993,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>16500</v>
+        <v>15900</v>
       </c>
       <c r="E14" s="3">
         <v>33600</v>
@@ -1106,7 +1106,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3066400</v>
+        <v>3067000</v>
       </c>
       <c r="E17" s="3">
         <v>2743500</v>
@@ -1154,7 +1154,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>101800</v>
+        <v>101200</v>
       </c>
       <c r="E18" s="3">
         <v>87200</v>
@@ -1222,7 +1222,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-62600</v>
+        <v>5600</v>
       </c>
       <c r="E20" s="3">
         <v>5900</v>
@@ -1270,7 +1270,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>291000</v>
+        <v>222200</v>
       </c>
       <c r="E21" s="3">
         <v>205700</v>
@@ -1317,8 +1317,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>7800</v>
       </c>
       <c r="E22" s="3">
         <v>7500</v>
@@ -1798,7 +1798,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>62600</v>
+        <v>-5600</v>
       </c>
       <c r="E32" s="3">
         <v>-5900</v>
@@ -2843,7 +2843,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>143500</v>
+        <v>143900</v>
       </c>
       <c r="E58" s="3">
         <v>48900</v>
@@ -2891,10 +2891,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>953800</v>
+        <v>1001200</v>
       </c>
       <c r="E59" s="3">
-        <v>889900</v>
+        <v>888900</v>
       </c>
       <c r="F59" s="3">
         <v>756100</v>
@@ -3896,7 +3896,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>126700</v>
+        <v>111000</v>
       </c>
       <c r="E83" s="3">
         <v>108200</v>
@@ -4184,7 +4184,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>753100</v>
+        <v>753600</v>
       </c>
       <c r="E89" s="3">
         <v>677700</v>
@@ -4396,7 +4396,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-217700</v>
+        <v>-218200</v>
       </c>
       <c r="E94" s="3">
         <v>3200</v>
